--- a/Figure 2/Figure 2-L.xlsx
+++ b/Figure 2/Figure 2-L.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wench\Desktop\英文写作\英文写作\工程菌KR32\论文需要上传的数据\iMetaOmics20260210\Figure 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B42A824F-860A-4EA2-A80B-653FEA78F041}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDEEF0F1-2580-4C6A-B44A-DB022A99F09D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-34650" yWindow="2080" windowWidth="15760" windowHeight="15580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28790" yWindow="4080" windowWidth="16730" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -144,16 +144,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
+      <color theme="1"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -176,11 +175,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -465,333 +465,336 @@
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.4140625" customWidth="1"/>
-    <col min="2" max="4" width="8.6640625" style="2"/>
+    <col min="2" max="4" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B1" s="2" t="s">
+      <c r="A1" s="2"/>
+      <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="3">
         <v>0.56891825799635831</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="3">
         <v>1.857250039788602</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="3">
         <v>7.2342624287029738</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="3">
         <v>1.0529534393334385</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="3">
         <v>1.3339383911317058</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="3">
         <v>2.5535939198797548</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="3">
         <v>1.0720058378890771</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="3">
         <v>0.70433911659608162</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="3">
         <v>3.3793672400233064</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="3">
         <v>0.8777868871610055</v>
       </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="3">
         <v>1.2699174571655607</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="3">
         <v>1.3061251509499425</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="3">
         <v>0.35941676090579916</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="3">
         <v>1.8804128061732908</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="3">
         <v>1.1886078401536113</v>
       </c>
-      <c r="D7" s="3"/>
+      <c r="D7" s="4"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="3">
         <v>3.2140412582886184</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="3">
         <v>0.6947242616839453</v>
       </c>
-      <c r="D8" s="3"/>
+      <c r="D8" s="4"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" s="3">
         <v>3.7655034672672332</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="3">
         <v>0.54276779424113863</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="3">
         <v>1.3213498935966199</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" s="3">
         <v>3.665451105112087</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="3">
         <v>0.50401393847673637</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10" s="3">
         <v>1.4629966828887397</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="3">
         <v>1.7947819754120142</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11" s="3">
         <v>0.61993366051463972</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D11" s="3">
         <v>0.20664892275673855</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12" s="3">
         <v>2.6364747876281092</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="3">
         <v>0.795429579005557</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12" s="3">
         <v>0.19527043151075582</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13" s="3">
         <v>2.4399131822862001</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" s="3">
         <v>0.28373758924371273</v>
       </c>
+      <c r="D13" s="3"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14" s="3">
         <v>3.3491802693924821</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="3">
         <v>0.87803575399589151</v>
       </c>
-      <c r="D14" s="3"/>
+      <c r="D14" s="4"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B15" s="3">
         <v>3.0659695535943081</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C15" s="3">
         <v>0.27369331957608034</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D15" s="3">
         <v>1.4862395505061421</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="2">
+      <c r="B16" s="3">
         <v>4.3322596836367593</v>
       </c>
-      <c r="C16" s="2">
+      <c r="C16" s="3">
         <v>0.98238235202154756</v>
       </c>
-      <c r="D16" s="2">
+      <c r="D16" s="3">
         <v>1.6039916891158756</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B17" s="3">
         <v>2.7484346954231738</v>
       </c>
-      <c r="C17" s="2">
+      <c r="C17" s="3">
         <v>0.53413526309609605</v>
       </c>
-      <c r="D17" s="2">
+      <c r="D17" s="3">
         <v>0.11436096996861859</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B18" s="2">
+      <c r="B18" s="3">
         <v>1.3002990794554037</v>
       </c>
-      <c r="C18" s="2">
+      <c r="C18" s="3">
         <v>0.94343163209895953</v>
       </c>
-      <c r="D18" s="2">
+      <c r="D18" s="3">
         <v>0.30601338582616333</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B19" s="2">
+      <c r="B19" s="3">
         <v>1.3168133354972733</v>
       </c>
-      <c r="C19" s="2">
+      <c r="C19" s="3">
         <v>0.5746131919444718</v>
       </c>
-      <c r="D19" s="2">
+      <c r="D19" s="3">
         <v>0.1674342603055218</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B20" s="2">
+      <c r="B20" s="3">
         <v>0.39470854362814806</v>
       </c>
-      <c r="C20" s="2">
+      <c r="C20" s="3">
         <v>0.39155659987953984</v>
       </c>
-      <c r="D20" s="2">
+      <c r="D20" s="3">
         <v>2.3919312998728031</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="s">
+      <c r="A21" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B21" s="2">
+      <c r="B21" s="3">
         <v>1.5388253086819415</v>
       </c>
-      <c r="C21" s="2">
+      <c r="C21" s="3">
         <v>0.78980726532972101</v>
       </c>
-      <c r="D21" s="2">
+      <c r="D21" s="3">
         <v>1.9842311848802145</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="1" t="s">
+      <c r="A22" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B22" s="3"/>
-      <c r="C22" s="2">
+      <c r="B22" s="4"/>
+      <c r="C22" s="3">
         <v>0.65628337096226064</v>
       </c>
-      <c r="D22" s="2">
+      <c r="D22" s="3">
         <v>2.0704634651381282</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
+      <c r="A23" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B23" s="2">
+      <c r="B23" s="3">
         <v>1.2635582035437909</v>
       </c>
-      <c r="C23" s="2">
+      <c r="C23" s="3">
         <v>0.59773854952956673</v>
       </c>
-      <c r="D23" s="3"/>
+      <c r="D23" s="4"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="1" t="s">
+      <c r="A24" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B24" s="2">
+      <c r="B24" s="3">
         <v>0.93405504926383753</v>
       </c>
-      <c r="C24" s="2">
+      <c r="C24" s="3">
         <v>0.36825334699850132</v>
       </c>
-      <c r="D24" s="3"/>
+      <c r="D24" s="4"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="1" t="s">
+      <c r="A25" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B25" s="2">
+      <c r="B25" s="3">
         <v>1.8148581326191602</v>
       </c>
-      <c r="C25" s="2">
+      <c r="C25" s="3">
         <v>0.59706156682320277</v>
       </c>
+      <c r="D25" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
